--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
@@ -467,22 +467,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.03101</v>
+        <v>17.16921</v>
       </c>
       <c r="D3" t="n">
-        <v>16.59295</v>
+        <v>16.89608</v>
       </c>
       <c r="E3" t="n">
-        <v>17.21176</v>
+        <v>16.94077</v>
       </c>
       <c r="F3" t="n">
-        <v>43.51611</v>
+        <v>42.74378</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05012</v>
+        <v>0.05103</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8587</v>
+        <v>1.84463</v>
       </c>
     </row>
     <row r="4">
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.9721</v>
+        <v>16.86206</v>
       </c>
       <c r="D4" t="n">
-        <v>16.73383</v>
+        <v>16.53102</v>
       </c>
       <c r="E4" t="n">
-        <v>16.92186</v>
+        <v>16.73465</v>
       </c>
       <c r="F4" t="n">
-        <v>42.62304</v>
+        <v>42.6787</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05036</v>
+        <v>0.0515</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83863</v>
+        <v>1.85011</v>
       </c>
     </row>
     <row r="5">
@@ -517,22 +517,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.71226</v>
+        <v>17.01949</v>
       </c>
       <c r="D5" t="n">
-        <v>16.65031</v>
+        <v>16.8397</v>
       </c>
       <c r="E5" t="n">
-        <v>16.8855</v>
+        <v>16.87944</v>
       </c>
       <c r="F5" t="n">
-        <v>43.05903</v>
+        <v>42.72166</v>
       </c>
       <c r="G5" t="n">
-        <v>0.052</v>
+        <v>0.0511</v>
       </c>
       <c r="H5" t="n">
-        <v>1.85013</v>
+        <v>1.83023</v>
       </c>
     </row>
     <row r="6">
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.9232</v>
+        <v>16.91295</v>
       </c>
       <c r="D6" t="n">
-        <v>17.03763</v>
+        <v>16.66286</v>
       </c>
       <c r="E6" t="n">
-        <v>16.94313</v>
+        <v>16.90416</v>
       </c>
       <c r="F6" t="n">
-        <v>43.1534</v>
+        <v>42.50143</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05052</v>
+        <v>0.05104</v>
       </c>
       <c r="H6" t="n">
-        <v>1.88824</v>
+        <v>1.87937</v>
       </c>
     </row>
     <row r="7">
@@ -567,22 +567,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.88291</v>
+        <v>16.88797</v>
       </c>
       <c r="D7" t="n">
-        <v>16.94399</v>
+        <v>16.78148</v>
       </c>
       <c r="E7" t="n">
-        <v>16.93331</v>
+        <v>16.79173</v>
       </c>
       <c r="F7" t="n">
-        <v>42.94258</v>
+        <v>43.43671</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05108</v>
+        <v>0.05164</v>
       </c>
       <c r="H7" t="n">
-        <v>1.83537</v>
+        <v>1.82771</v>
       </c>
     </row>
     <row r="8">
@@ -592,22 +592,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.99122</v>
+        <v>17.14699</v>
       </c>
       <c r="D8" t="n">
-        <v>16.83635</v>
+        <v>16.94735</v>
       </c>
       <c r="E8" t="n">
-        <v>16.78454</v>
+        <v>17.03711</v>
       </c>
       <c r="F8" t="n">
-        <v>43.37506</v>
+        <v>43.01782</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05181</v>
+        <v>0.05138</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82963</v>
+        <v>1.84761</v>
       </c>
     </row>
     <row r="9">
@@ -617,22 +617,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.16964</v>
+        <v>16.95951</v>
       </c>
       <c r="D9" t="n">
-        <v>16.7084</v>
+        <v>16.80919</v>
       </c>
       <c r="E9" t="n">
-        <v>16.71313</v>
+        <v>16.9005</v>
       </c>
       <c r="F9" t="n">
-        <v>43.46427</v>
+        <v>43.14506</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05162</v>
+        <v>0.05036</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8585</v>
+        <v>1.81039</v>
       </c>
     </row>
     <row r="10">
@@ -642,22 +642,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.02638</v>
+        <v>16.88349</v>
       </c>
       <c r="D10" t="n">
-        <v>16.93568</v>
+        <v>16.84413</v>
       </c>
       <c r="E10" t="n">
-        <v>16.85694</v>
+        <v>16.84774</v>
       </c>
       <c r="F10" t="n">
-        <v>43.06988</v>
+        <v>43.64999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05049</v>
+        <v>0.05112</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82194</v>
+        <v>1.84134</v>
       </c>
     </row>
     <row r="11">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17.0928</v>
+        <v>17.03633</v>
       </c>
       <c r="D11" t="n">
-        <v>16.77261</v>
+        <v>16.85556</v>
       </c>
       <c r="E11" t="n">
-        <v>17.1815</v>
+        <v>16.96367</v>
       </c>
       <c r="F11" t="n">
-        <v>42.90616</v>
+        <v>43.82948</v>
       </c>
       <c r="G11" t="n">
-        <v>0.05044</v>
+        <v>0.05069</v>
       </c>
       <c r="H11" t="n">
-        <v>1.86491</v>
+        <v>1.832</v>
       </c>
     </row>
     <row r="12">
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.61136</v>
+        <v>0.61929</v>
       </c>
       <c r="D13" t="n">
-        <v>1.12171</v>
+        <v>1.11362</v>
       </c>
     </row>
     <row r="14">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.60411</v>
+        <v>0.60572</v>
       </c>
       <c r="D14" t="n">
-        <v>1.12276</v>
+        <v>1.15559</v>
       </c>
     </row>
     <row r="15">
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.62923</v>
+        <v>0.61832</v>
       </c>
       <c r="D15" t="n">
-        <v>1.11487</v>
+        <v>1.11558</v>
       </c>
     </row>
     <row r="16">
@@ -748,10 +748,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.60543</v>
+        <v>0.6142300000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>1.11205</v>
+        <v>1.15119</v>
       </c>
     </row>
     <row r="17">
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.60658</v>
+        <v>0.61972</v>
       </c>
       <c r="D17" t="n">
-        <v>1.13369</v>
+        <v>1.11229</v>
       </c>
     </row>
     <row r="18">
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.61968</v>
+        <v>0.61416</v>
       </c>
       <c r="D18" t="n">
-        <v>1.13984</v>
+        <v>1.11473</v>
       </c>
     </row>
     <row r="19">
@@ -787,10 +787,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.6087900000000001</v>
+        <v>0.62073</v>
       </c>
       <c r="D19" t="n">
-        <v>1.13155</v>
+        <v>1.13734</v>
       </c>
     </row>
     <row r="20">
@@ -800,10 +800,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.61073</v>
+        <v>0.60907</v>
       </c>
       <c r="D20" t="n">
-        <v>1.13019</v>
+        <v>1.12473</v>
       </c>
     </row>
     <row r="21">
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.6085199999999999</v>
+        <v>0.61069</v>
       </c>
       <c r="D21" t="n">
-        <v>1.10821</v>
+        <v>1.11806</v>
       </c>
     </row>
     <row r="22">
@@ -873,28 +873,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.77445</v>
+        <v>0.74488</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08276</v>
+        <v>0.08054</v>
       </c>
       <c r="E23" t="n">
-        <v>0.61916</v>
+        <v>0.60958</v>
       </c>
       <c r="F23" t="n">
-        <v>0.96262</v>
+        <v>0.96348</v>
       </c>
       <c r="G23" t="n">
-        <v>0.11078</v>
+        <v>0.11184</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00762</v>
+        <v>0.00761</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09521</v>
+        <v>0.09399</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1248</v>
+        <v>0.12788</v>
       </c>
     </row>
     <row r="24">
@@ -904,28 +904,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.75848</v>
+        <v>0.76729</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08232</v>
+        <v>0.08255</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6091800000000001</v>
+        <v>0.62553</v>
       </c>
       <c r="F24" t="n">
-        <v>0.95434</v>
+        <v>0.96998</v>
       </c>
       <c r="G24" t="n">
-        <v>0.11125</v>
+        <v>0.10862</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00766</v>
+        <v>0.00772</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09324</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.12638</v>
+        <v>0.12698</v>
       </c>
     </row>
     <row r="25">
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.75775</v>
+        <v>0.76962</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08109</v>
+        <v>0.08470999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0.621</v>
+        <v>0.60973</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9769600000000001</v>
+        <v>0.98404</v>
       </c>
       <c r="G25" t="n">
-        <v>0.10853</v>
+        <v>0.11204</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00769</v>
+        <v>0.00773</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09653</v>
+        <v>0.09376</v>
       </c>
       <c r="J25" t="n">
-        <v>0.12863</v>
+        <v>0.1287</v>
       </c>
     </row>
     <row r="26">
@@ -966,28 +966,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.73742</v>
+        <v>0.76623</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0815</v>
+        <v>0.08153000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>0.60897</v>
+        <v>0.61699</v>
       </c>
       <c r="F26" t="n">
-        <v>0.96438</v>
+        <v>0.97571</v>
       </c>
       <c r="G26" t="n">
-        <v>0.11239</v>
+        <v>0.11161</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00756</v>
+        <v>0.00775</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09266000000000001</v>
+        <v>0.09404999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.12594</v>
+        <v>0.12716</v>
       </c>
     </row>
     <row r="27">
@@ -997,28 +997,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.77306</v>
+        <v>0.75659</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08139</v>
+        <v>0.08164</v>
       </c>
       <c r="E27" t="n">
-        <v>0.62574</v>
+        <v>0.61265</v>
       </c>
       <c r="F27" t="n">
-        <v>0.96566</v>
+        <v>0.97279</v>
       </c>
       <c r="G27" t="n">
-        <v>0.10855</v>
+        <v>0.11269</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00751</v>
+        <v>0.00774</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09317</v>
+        <v>0.09505</v>
       </c>
       <c r="J27" t="n">
-        <v>0.12758</v>
+        <v>0.12642</v>
       </c>
     </row>
     <row r="28">
@@ -1028,28 +1028,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.76662</v>
+        <v>0.77565</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08308</v>
+        <v>0.08089</v>
       </c>
       <c r="E28" t="n">
-        <v>0.61067</v>
+        <v>0.60701</v>
       </c>
       <c r="F28" t="n">
-        <v>0.96978</v>
+        <v>0.97464</v>
       </c>
       <c r="G28" t="n">
-        <v>0.10952</v>
+        <v>0.11256</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00766</v>
+        <v>0.00751</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09195</v>
+        <v>0.09261999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.12966</v>
+        <v>0.12598</v>
       </c>
     </row>
     <row r="29">
@@ -1059,28 +1059,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.75448</v>
+        <v>0.77128</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08304</v>
+        <v>0.08258</v>
       </c>
       <c r="E29" t="n">
-        <v>0.59391</v>
+        <v>0.6189</v>
       </c>
       <c r="F29" t="n">
-        <v>0.98349</v>
+        <v>0.96018</v>
       </c>
       <c r="G29" t="n">
-        <v>0.11069</v>
+        <v>0.10821</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00778</v>
+        <v>0.00769</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09277000000000001</v>
+        <v>0.09472</v>
       </c>
       <c r="J29" t="n">
-        <v>0.12557</v>
+        <v>0.12889</v>
       </c>
     </row>
     <row r="30">
@@ -1090,28 +1090,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.76248</v>
+        <v>0.73904</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08230999999999999</v>
+        <v>0.08135000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>0.62635</v>
+        <v>0.60908</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9753500000000001</v>
+        <v>0.96978</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1111</v>
+        <v>0.11071</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00757</v>
+        <v>0.00776</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09211999999999999</v>
+        <v>0.09271</v>
       </c>
       <c r="J30" t="n">
-        <v>0.12833</v>
+        <v>0.12788</v>
       </c>
     </row>
     <row r="31">
@@ -1121,28 +1121,28 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.75103</v>
+        <v>0.76442</v>
       </c>
       <c r="D31" t="n">
-        <v>0.08118</v>
+        <v>0.08049000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>0.61537</v>
+        <v>0.61778</v>
       </c>
       <c r="F31" t="n">
-        <v>0.97812</v>
+        <v>0.99878</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1103</v>
+        <v>0.11094</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00763</v>
+        <v>0.00766</v>
       </c>
       <c r="I31" t="n">
-        <v>0.09664</v>
+        <v>0.09407</v>
       </c>
       <c r="J31" t="n">
-        <v>0.12862</v>
+        <v>0.12773</v>
       </c>
     </row>
   </sheetData>
